--- a/my_programs/下载论文.xlsx
+++ b/my_programs/下载论文.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>时间</t>
   </si>
@@ -68,7 +68,7 @@
     <t>图片：targets/edge.png|q3</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>图片：targets/plus.png|up</t>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>回车</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>按键松开</t>
@@ -1187,7 +1184,7 @@
     <col min="9" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1324,10 +1321,10 @@
     </row>
     <row r="10" s="2" customFormat="1" spans="1:8">
       <c r="A10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>21</v>
@@ -1340,16 +1337,16 @@
     </row>
     <row r="11" s="2" customFormat="1" spans="1:8">
       <c r="A11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="9"/>
@@ -1362,26 +1359,26 @@
         <v>15</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="9"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="1:8">
       <c r="B13" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="1:8">
       <c r="B14" s="10" t="s">
         <v>20</v>
       </c>
@@ -1393,7 +1390,7 @@
     <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>21</v>
@@ -1407,10 +1404,10 @@
     <row r="16" s="2" customFormat="1" spans="1:8">
       <c r="A16" s="3"/>
       <c r="B16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>

--- a/my_programs/下载论文.xlsx
+++ b/my_programs/下载论文.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>时间</t>
   </si>
@@ -53,7 +53,7 @@
     <t>循环1{</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t>0</t>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>}</t>
+  </si>
+  <si>
+    <t>鼠标点击</t>
+  </si>
+  <si>
+    <t>右键</t>
   </si>
 </sst>
 </file>
@@ -1417,8 +1423,12 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:8">
       <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
